--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -9,15 +9,15 @@
   </bookViews>
   <sheets>
     <sheet name="Pay Calculator" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Pay Notes" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Pay Guide" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Settings &amp; Rates" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Tax Engine" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Pay Calculator'!$A$1:$J$99</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'Pay Calculator'!$1:$2</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Pay Notes'!$A$1:$J$51</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Pay Notes'!$1:$2</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Pay Guide'!$A$1:$J$51</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Pay Guide'!$1:$2</definedName>
     <definedName function="false" hidden="false" name="BaseRate" vbProcedure="false">'Tax Engine'!$F$5</definedName>
     <definedName function="false" hidden="false" name="ConcCap" vbProcedure="false">'Settings &amp; Rates'!$B$44</definedName>
     <definedName function="false" hidden="false" name="ContribTax" vbProcedure="false">'Settings &amp; Rates'!$B$42</definedName>
@@ -528,7 +528,7 @@
     <t xml:space="preserve">Leave the payslip column blank when you are not reconciling. A mismatch usually means a rate on Settings &amp; Rates is stale, or payroll treats an allowance differently — see block E for the clause each rate comes from.</t>
   </si>
   <si>
-    <t xml:space="preserve">PayCalc V19 · pay scale award 01.09.2025 · tax tables ATO 01.07.2026 · plain-English guide on the Pay Notes tab · rates, sources &amp; incoming changes on Settings &amp; Rates</t>
+    <t xml:space="preserve">PayCalc V19 · pay scale award 01.09.2025 · tax tables ATO 01.07.2026 · plain-English guide on the Pay Guide tab · rates, sources &amp; incoming changes on Settings &amp; Rates</t>
   </si>
   <si>
     <t xml:space="preserve">PAY  NOTES</t>
@@ -1023,7 +1023,7 @@
     <t xml:space="preserve">OFFER 16.07.2026 — not yet certified</t>
   </si>
   <si>
-    <t xml:space="preserve">Employer Offer dated 16.07.2026 (3-year term, expires 31.07.2029). Three increases: 1 Aug 2026 = 3.5% (3% + 0.5% CPI uplift, already triggered), 1 Aug 2027 = 2.5%, 1 Aug 2028 = 2.5%. The FIRST rise applies to the higher of Award or Agreement — i.e. the Award rate (cl 2.18(6) retained). Allowances that track wages rise by the same %. CONDITIONAL: all unions must agree in-principle by 31.08.2026 to hold the 1 Aug date, else it shifts to the first of the month agreement is reached. NOT applied yet — do not change rates until certified. When certified, the EBA rise builds a SEPARATE agreement ladder — it must NOT be added to block A. Block A is the AWARD ladder; it moves only at a State Wage Case / reprint (~1 Sep). The certification (~1 Aug) and the SWC (~1 Sep) are only 31 days apart, so bumping block A on certification would be overwritten a month later = double-bump. Correct method: 1) build an Agreement-rate column = (award rate at 31.07.2026) × the agreed % for each row; 2) operational rate + $379 cap × same %; 3) set pay = MAX(award, agreement) per row (cl 2.18(6)); 4) block A itself changes ONLY at the SWC/reprint; 5) pull the Rates-checked-until tripwire back to the first-rise date (1 Aug if unions agree by 31 Aug); 6) footer date. Do NOT index: retention (cl 2.12(5) — not subject to annual increase, stays $45.00), shift % (a % of earnings — self-indexes; only change if the certified % changes), qualification (cl 4.2 — no indexation clause, hold pending certified text), in-charge/laundry (move with the award/SWC, not the EBA). YEARS 2-3: each 1 Aug, agreement ladder × 1.025 applied to the PRECEDING AGREEMENT rate (offer wording), NOT the award. After each 1 Sep SWC the award ladder moves independently — keep BOTH ladders live and re-check the MAX winner per row. Caution: if an SWC is ever a flat dollar amount or tiered (not a flat %), the winning ladder can differ by classification — don't assume a blanket MAX. If certification lands after 1 Aug, the first rise backdates and arrives lump-sum-taxed — use the 'Other taxable earnings' row and point to the Pay Notes lump-sum explainer.</t>
+    <t xml:space="preserve">Employer Offer dated 16.07.2026 (3-year term, expires 31.07.2029). Three increases: 1 Aug 2026 = 3.5% (3% + 0.5% CPI uplift, already triggered), 1 Aug 2027 = 2.5%, 1 Aug 2028 = 2.5%. The FIRST rise applies to the higher of Award or Agreement — i.e. the Award rate (cl 2.18(6) retained). Allowances that track wages rise by the same %. CONDITIONAL: all unions must agree in-principle by 31.08.2026 to hold the 1 Aug date, else it shifts to the first of the month agreement is reached. NOT applied yet — do not change rates until certified. When certified, the EBA rise builds a SEPARATE agreement ladder — it must NOT be added to block A. Block A is the AWARD ladder; it moves only at a State Wage Case / reprint (~1 Sep). The certification (~1 Aug) and the SWC (~1 Sep) are only 31 days apart, so bumping block A on certification would be overwritten a month later = double-bump. Correct method: 1) build an Agreement-rate column = (award rate at 31.07.2026) × the agreed % for each row; 2) operational rate + $379 cap × same %; 3) set pay = MAX(award, agreement) per row (cl 2.18(6)); 4) block A itself changes ONLY at the SWC/reprint; 5) pull the Rates-checked-until tripwire back to the first-rise date (1 Aug if unions agree by 31 Aug); 6) footer date. Do NOT index: retention (cl 2.12(5) — not subject to annual increase, stays $45.00), shift % (a % of earnings — self-indexes; only change if the certified % changes), qualification (cl 4.2 — no indexation clause, hold pending certified text), in-charge/laundry (move with the award/SWC, not the EBA). YEARS 2-3: each 1 Aug, agreement ladder × 1.025 applied to the PRECEDING AGREEMENT rate (offer wording), NOT the award. After each 1 Sep SWC the award ladder moves independently — keep BOTH ladders live and re-check the MAX winner per row. Caution: if an SWC is ever a flat dollar amount or tiered (not a flat %), the winning ladder can differ by classification — don't assume a blanket MAX. If certification lands after 1 Aug, the first rise backdates and arrives lump-sum-taxed — use the 'Other taxable earnings' row and point to the Pay Guide lump-sum explainer.</t>
   </si>
   <si>
     <t xml:space="preserve">State Wage Case 2026</t>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -531,7 +531,7 @@
     <t xml:space="preserve">PayCalc V19 · pay scale award 01.09.2025 · tax tables ATO 01.07.2026 · plain-English guide on the Pay Guide tab · rates, sources &amp; incoming changes on Settings &amp; Rates</t>
   </si>
   <si>
-    <t xml:space="preserve">PAY  NOTES</t>
+    <t xml:space="preserve">PAY  GUIDE</t>
   </si>
   <si>
     <t xml:space="preserve">How your pay actually works — real rates, what applies when, and where each rule comes from (award = YDC Award 2016 · EBA = CB/2023/139)</t>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -645,7 +645,7 @@
     <t xml:space="preserve">Casual loading</t>
   </si>
   <si>
-    <t xml:space="preserve">25% on top of the permanent rate (Award cl 8.3(c)), paid INSTEAD of annual, sick and long-service leave, notice and redundancy. It’s part of your ordinary rate, so shift allowance and super are calculated on the loaded rate.</t>
+    <t xml:space="preserve">25% on top of the permanent rate (Award cl 8.3(c)), paid INSTEAD of annual and sick leave, notice and redundancy. It’s part of your ordinary rate, so shift allowance and super are calculated on the loaded rate.</t>
   </si>
   <si>
     <t xml:space="preserve">Minimum engagements</t>
@@ -684,7 +684,7 @@
     <t xml:space="preserve">Casuals &amp; leave</t>
   </si>
   <si>
-    <t xml:space="preserve">No paid leave — the 25% loading is the trade (Award cl 8.3(e)). The leave boxes on the calculator only apply to permanent staff.</t>
+    <t xml:space="preserve">Normally no paid leave — the 25% loading is the trade (Award cl 8.3(e)). Long service and special leave can still be payable in particular circumstances; check your own entitlement before relying on a leave figure. Note: the leave boxes in this workbook apply to permanent staff only — the website calculator is the one that accepts casual long service and special leave.</t>
   </si>
   <si>
     <t xml:space="preserve">⑤   TAX &amp; SUPER</t>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -94,7 +94,7 @@
     <definedName function="false" hidden="false" name="STSLChoice" vbProcedure="false">'Pay Calculator'!$E$61</definedName>
     <definedName function="false" hidden="false" name="STSL_FN" vbProcedure="false">'Tax Engine'!$F$19</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr fullCalcOnLoad="1" iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -591,7 +591,7 @@
     <t xml:space="preserve">Retention</t>
   </si>
   <si>
-    <t xml:space="preserve">$45.00/fn (= $0.5921/hr × 76) once you’ve done 2 years’ continuous service (EBA cl 2.12). Doesn’t index with pay rises (cl 2.12(5)). Keeps being paid on all paid leave, sick included. Note: on paper it’s all-purpose (cl 2.12(2)(i) — ‘subject to any applicable overtime or penalty rates’); the calculator pays it flat to 76 hours (site practice), so on an overtime-heavy fortnight it’s worth checking with a delegate.</t>
+    <t xml:space="preserve">$45.00/fn (= $0.5921/hr × 76) once you’ve done 2 years’ continuous service (EBA cl 2.12). Doesn’t index with pay rises (cl 2.12(5)). Keeps being paid on all paid leave, sick included. Note: on paper it’s all-purpose (cl 2.12(2)(i) — ‘subject to any applicable overtime or penalty rates’); the calculator pays it flat to 76 hours, matching the payslip element "YD Retent 76", so on an overtime-heavy fortnight it’s worth checking with a delegate.</t>
   </si>
   <si>
     <t xml:space="preserve">Laundry</t>
@@ -807,7 +807,7 @@
     <t xml:space="preserve">L6-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Award rates, effective 01.09.2025 — verified against the QIRC 01.09.2025 award reprint (all 15 rows round exactly to the published fortnightly $). Hourly = fortnightly ÷ 76; casual = permanent × 1.25 (all three columns reconcile exactly). The award floor sits above the 01.08.2025 EBA rates and prevails under EBA cl 2.18(6). Custom rates are typed straight on the calculator. Update when the new agreement or the 2026 State Wage Case lands — see block E.</t>
+    <t xml:space="preserve">Award rates, effective 01.09.2025 — verified against the QIRC 01.09.2025 award reprint (all 15 rows round exactly to the published fortnightly $). Hourly = fortnightly ÷ 76; casual = permanent × 1.25 (all three columns reconcile exactly). The fortnightly salary is a whole dollar: the 2025 wage case applied 3.5% to the old whole-dollar salary and rounded back to the nearest dollar, e.g. L4-4 $2,993 → $3,097.755 → $3,098 → $40.76316/hr. Cross-checked against a real payslip (11–24 Jul 2026), which pays L4-4 at $40.76316 and L5-1 at $41.78947 — both exact. Keep the rounding when the next wage case lands. The award floor sits above the 01.08.2025 EBA rates and prevails under EBA cl 2.18(6). Custom rates are typed straight on the calculator. Update when the new agreement or the 2026 State Wage Case lands — see block E.</t>
   </si>
   <si>
     <t xml:space="preserve">B · ALLOWANCE RATES</t>
@@ -861,7 +861,7 @@
     <t xml:space="preserve">EBA cl 2.10(3)(ii) — rate from 01.08.2025 (prev. 4.8415), max $379.00/fn = 76 ordinary hours (the calculator caps at 76). Set the rate to 0 to switch off.</t>
   </si>
   <si>
-    <t xml:space="preserve">EBA cl 2.12 — $45.00/fn ÷ 76, after 2 years' service. Applied to ordinary hours up to 76 (site practice). Yes/No toggle lives on the calculator page.</t>
+    <t xml:space="preserve">EBA cl 2.12 — $45.00/fn ÷ 76, after 2 years' service. Applied to ordinary hours up to 76 — confirmed by a real payslip, where the element is literally named "YD Retent 76" and pays $0.59210/hr on hours worked. Casuals get it pro-rata (EBA cl 2.12(4)). Yes/No toggle lives on the calculator page.</t>
   </si>
   <si>
     <t xml:space="preserve">Award cl 13.6(b) — $6.10/fn ÷ 76, CPI-adjusted at the 2025 State Wage Case (was $6.00). Set 0 to switch off. (Separate soiled-linen allowance cl 2.11 is out of scope — it applies to OO2 Laundry Assistant / OO3 Laundry Supervisor roles only, not operational shiftworkers.)</t>
@@ -900,7 +900,7 @@
     <t xml:space="preserve">Employer super rate</t>
   </si>
   <si>
-    <t xml:space="preserve">Superannuation (State Public Sector) Regulation 2023 s 12 — 12.75% of salary, defined as earnings for ordinary hours PLUS shift loadings PLUS payments made on paid leave. Overtime is out; so is laundry (an expense reimbursement, not OTE). Since 01.07.2023 you receive the full 12.75% whether or not you make the member contribution.</t>
+    <t xml:space="preserve">Superannuation (State Public Sector) Regulation 2023 s 12 — 12.75% of salary, defined as earnings for ordinary hours PLUS shift loadings PLUS payments made on paid leave. Overtime is out. Laundry IS in: on a real payslip (11–24 Jul 2026) the employer contribution came to exactly 12.75% of the full gross, laundry included. Since 01.07.2023 you receive the full 12.75% whether or not you make the member contribution.</t>
   </si>
   <si>
     <t xml:space="preserve">Super contributions tax</t>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF(OR($B$6="Custom",$B$6=""),"",IFERROR(INDEX(PayScaleRates,MATCH($B$6,PayScaleNames,0),IF($B$5="Casual",2,1)),""))</f>
-        <v>35.80276</v>
+        <v>35.80263</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="8" t="s">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF(OR($B$7="None",$B$7="Custom",$B$7=""),"",IFERROR(INDEX(PayScaleRates,MATCH($B$7,PayScaleNames,0),IF($B$5="Casual",2,1)),""))</f>
-        <v>41.79487</v>
+        <v>41.78947</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="8" t="s">
@@ -5687,15 +5687,15 @@
         <v>218</v>
       </c>
       <c r="B6" s="96" t="n">
-        <v>33.70553</v>
+        <v>33.71053</v>
       </c>
       <c r="C6" s="97" t="n">
         <f aca="false">B6*1.25</f>
-        <v>42.1319125</v>
+        <v>42.1381625</v>
       </c>
       <c r="D6" s="98" t="n">
         <f aca="false">B6*76</f>
-        <v>2561.62028</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5703,15 +5703,15 @@
         <v>219</v>
       </c>
       <c r="B7" s="96" t="n">
-        <v>34.35921</v>
+        <v>34.35526</v>
       </c>
       <c r="C7" s="97" t="n">
         <f aca="false">B7*1.25</f>
-        <v>42.9490125</v>
+        <v>42.944075</v>
       </c>
       <c r="D7" s="98" t="n">
         <f aca="false">B7*76</f>
-        <v>2611.29996</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5719,15 +5719,15 @@
         <v>220</v>
       </c>
       <c r="B8" s="96" t="n">
-        <v>35.08105</v>
+        <v>35.07895</v>
       </c>
       <c r="C8" s="97" t="n">
         <f aca="false">B8*1.25</f>
-        <v>43.8513125</v>
+        <v>43.8486875</v>
       </c>
       <c r="D8" s="98" t="n">
         <f aca="false">B8*76</f>
-        <v>2666.1598</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5735,15 +5735,15 @@
         <v>7</v>
       </c>
       <c r="B9" s="96" t="n">
-        <v>35.80276</v>
+        <v>35.80263</v>
       </c>
       <c r="C9" s="97" t="n">
         <f aca="false">B9*1.25</f>
-        <v>44.75345</v>
+        <v>44.7532875</v>
       </c>
       <c r="D9" s="98" t="n">
         <f aca="false">B9*76</f>
-        <v>2721.00976</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5751,15 +5751,15 @@
         <v>221</v>
       </c>
       <c r="B10" s="96" t="n">
-        <v>37.24632</v>
+        <v>37.25</v>
       </c>
       <c r="C10" s="97" t="n">
         <f aca="false">B10*1.25</f>
-        <v>46.5579</v>
+        <v>46.5625</v>
       </c>
       <c r="D10" s="98" t="n">
         <f aca="false">B10*76</f>
-        <v>2830.72032</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5767,15 +5767,15 @@
         <v>222</v>
       </c>
       <c r="B11" s="96" t="n">
-        <v>38.4175</v>
+        <v>38.42105</v>
       </c>
       <c r="C11" s="97" t="n">
         <f aca="false">B11*1.25</f>
-        <v>48.021875</v>
+        <v>48.0263125</v>
       </c>
       <c r="D11" s="98" t="n">
         <f aca="false">B11*76</f>
-        <v>2919.73</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5783,15 +5783,15 @@
         <v>223</v>
       </c>
       <c r="B12" s="96" t="n">
-        <v>39.61592</v>
+        <v>39.61842</v>
       </c>
       <c r="C12" s="97" t="n">
         <f aca="false">B12*1.25</f>
-        <v>49.5199</v>
+        <v>49.523025</v>
       </c>
       <c r="D12" s="98" t="n">
         <f aca="false">B12*76</f>
-        <v>3010.80992</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5799,15 +5799,15 @@
         <v>224</v>
       </c>
       <c r="B13" s="96" t="n">
-        <v>40.75987</v>
+        <v>40.76316</v>
       </c>
       <c r="C13" s="97" t="n">
         <f aca="false">B13*1.25</f>
-        <v>50.9498375</v>
+        <v>50.95395</v>
       </c>
       <c r="D13" s="98" t="n">
         <f aca="false">B13*76</f>
-        <v>3097.75012</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5815,15 +5815,15 @@
         <v>10</v>
       </c>
       <c r="B14" s="96" t="n">
-        <v>41.79487</v>
+        <v>41.78947</v>
       </c>
       <c r="C14" s="97" t="n">
         <f aca="false">B14*1.25</f>
-        <v>52.2435875</v>
+        <v>52.2368375</v>
       </c>
       <c r="D14" s="98" t="n">
         <f aca="false">B14*76</f>
-        <v>3176.41012</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5831,15 +5831,15 @@
         <v>225</v>
       </c>
       <c r="B15" s="96" t="n">
-        <v>43.10224</v>
+        <v>43.10526</v>
       </c>
       <c r="C15" s="97" t="n">
         <f aca="false">B15*1.25</f>
-        <v>53.8778</v>
+        <v>53.881575</v>
       </c>
       <c r="D15" s="98" t="n">
         <f aca="false">B15*76</f>
-        <v>3275.77024</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5847,15 +5847,15 @@
         <v>226</v>
       </c>
       <c r="B16" s="96" t="n">
-        <v>44.49132</v>
+        <v>44.48684</v>
       </c>
       <c r="C16" s="97" t="n">
         <f aca="false">B16*1.25</f>
-        <v>55.61415</v>
+        <v>55.60855</v>
       </c>
       <c r="D16" s="98" t="n">
         <f aca="false">B16*76</f>
-        <v>3381.34032</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5863,15 +5863,15 @@
         <v>227</v>
       </c>
       <c r="B17" s="96" t="n">
-        <v>45.82592</v>
+        <v>45.82895</v>
       </c>
       <c r="C17" s="97" t="n">
         <f aca="false">B17*1.25</f>
-        <v>57.2824</v>
+        <v>57.2861875</v>
       </c>
       <c r="D17" s="98" t="n">
         <f aca="false">B17*76</f>
-        <v>3482.76992</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5879,15 +5879,15 @@
         <v>228</v>
       </c>
       <c r="B18" s="96" t="n">
-        <v>47.75974</v>
+        <v>47.76316</v>
       </c>
       <c r="C18" s="97" t="n">
         <f aca="false">B18*1.25</f>
-        <v>59.699675</v>
+        <v>59.70395</v>
       </c>
       <c r="D18" s="98" t="n">
         <f aca="false">B18*76</f>
-        <v>3629.74024</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="D19" s="98" t="n">
         <f aca="false">B19*76</f>
-        <v>3726.00032</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5911,15 +5911,15 @@
         <v>230</v>
       </c>
       <c r="B20" s="96" t="n">
-        <v>50.22474</v>
+        <v>50.22368</v>
       </c>
       <c r="C20" s="97" t="n">
         <f aca="false">B20*1.25</f>
-        <v>62.780925</v>
+        <v>62.7796</v>
       </c>
       <c r="D20" s="98" t="n">
         <f aca="false">B20*76</f>
-        <v>3817.08024</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="F5" s="112" t="n">
         <f aca="false">IF(OR('Pay Calculator'!$B$6="Custom",'Pay Calculator'!$B$6=""),N('Pay Calculator'!$D$6),IFERROR(INDEX(PayScaleRates,MATCH('Pay Calculator'!$B$6,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$6)))</f>
-        <v>35.80276</v>
+        <v>35.80263</v>
       </c>
       <c r="H5" s="111" t="s">
         <v>323</v>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="F6" s="112" t="n">
         <f aca="false">IF('Pay Calculator'!$B$7="None",0,IF(OR('Pay Calculator'!$B$7="Custom",'Pay Calculator'!$B$7=""),N('Pay Calculator'!$D$7),IFERROR(INDEX(PayScaleRates,MATCH('Pay Calculator'!$B$7,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$7))))</f>
-        <v>41.79487</v>
+        <v>41.78947</v>
       </c>
       <c r="H6" s="111" t="s">
         <v>326</v>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -684,7 +684,7 @@
     <t xml:space="preserve">Casuals &amp; leave</t>
   </si>
   <si>
-    <t xml:space="preserve">Normally no paid leave — the 25% loading is the trade (Award cl 8.3(e)). Long service and special leave can still be payable in particular circumstances; check your own entitlement before relying on a leave figure. Note: the leave boxes in this workbook apply to permanent staff only — the website calculator is the one that accepts casual long service and special leave.</t>
+    <t xml:space="preserve">Normally no paid leave — the 25% loading is the trade (Award cl 8.3(e)). Long service leave is the exception: it is expressly extended to casuals (Award cl 8.3(h) and cl 22(a)) and is paid at the loaded casual rate. Special leave is NOT payable to casuals — the paid entitlement exists only under Special Leave Directive 12/24, whose cl 4.2 says the directive does not apply to casual employees except for unpaid Bereavement and unpaid Compassionate Leave. Check your own entitlement before relying on a leave figure. Note: the leave boxes in this workbook apply to permanent staff only — the website calculator is the one that accepts casual long service leave.</t>
   </si>
   <si>
     <t xml:space="preserve">⑤   TAX &amp; SUPER</t>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -684,7 +684,7 @@
     <t xml:space="preserve">Casuals &amp; leave</t>
   </si>
   <si>
-    <t xml:space="preserve">Normally no paid leave — the 25% loading is the trade (Award cl 8.3(e)). Long service leave is the exception: it is expressly extended to casuals (Award cl 8.3(h) and cl 22(a)) and is paid at the loaded casual rate. Special leave is NOT payable to casuals — the paid entitlement exists only under Special Leave Directive 12/24, whose cl 4.2 says the directive does not apply to casual employees except for unpaid Bereavement and unpaid Compassionate Leave. Check your own entitlement before relying on a leave figure. Note: the leave boxes in this workbook apply to permanent staff only — the website calculator is the one that accepts casual long service leave.</t>
+    <t xml:space="preserve">Normally no paid leave — the 25% loading is the trade (Award cl 8.3(e)). Long service leave is the real exception: expressly extended to casuals (Award cl 8.3(h) and cl 22(a)) and paid at the loaded casual rate. Special leave is a different case — you are probably NOT entitled to it: the paid entitlement exists only under Special Leave Directive 12/24, whose cl 4.2 says the directive does not apply to casual employees except for unpaid Bereavement and unpaid Compassionate Leave. It is still accepted on the website calculator because it does occasionally get approved and paid anyway, so a payslip showing it can be reconciled — but do not plan on it. Check your own entitlement before relying on a leave figure. Note: the leave boxes in this workbook apply to permanent staff only — the website calculator is the one that accepts casual long service and special leave.</t>
   </si>
   <si>
     <t xml:space="preserve">⑤   TAX &amp; SUPER</t>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -684,7 +684,7 @@
     <t xml:space="preserve">Casuals &amp; leave</t>
   </si>
   <si>
-    <t xml:space="preserve">Normally no paid leave — the 25% loading is the trade (Award cl 8.3(e)). Long service leave is the real exception: expressly extended to casuals (Award cl 8.3(h) and cl 22(a)) and paid at the loaded casual rate. Special leave is a different case — you are probably NOT entitled to it: the paid entitlement exists only under Special Leave Directive 12/24, whose cl 4.2 says the directive does not apply to casual employees except for unpaid Bereavement and unpaid Compassionate Leave. It is still accepted on the website calculator because it does occasionally get approved and paid anyway, so a payslip showing it can be reconciled — but do not plan on it. Check your own entitlement before relying on a leave figure. Note: the leave boxes in this workbook apply to permanent staff only — the website calculator is the one that accepts casual long service and special leave.</t>
+    <t xml:space="preserve">Normally no paid leave — the 25% loading is the trade (Award cl 8.3(e)). Long service leave is the real exception: expressly extended to casuals (Award cl 8.3(h) and cl 22(a)) and paid at the loaded casual rate. Special leave is a different case — you are probably NOT entitled to it: the paid entitlement exists only under Special Leave Directive 12/24, whose cl 4.2 says the directive does not apply to casual employees except for unpaid Bereavement and unpaid Compassionate Leave. It is still accepted here and on the website because it does occasionally get approved and paid anyway, so a payslip showing it can be reconciled — but do not plan on it. Check your own entitlement before relying on a leave figure. Note: as at 26.07.2026 this workbook matches the website — pick Casual and the sick/carer's and annual boxes pay nothing, while long service and special leave still pay at the loaded casual rate.</t>
   </si>
   <si>
     <t xml:space="preserve">⑤   TAX &amp; SUPER</t>
@@ -870,7 +870,7 @@
     <t xml:space="preserve">$ / night</t>
   </si>
   <si>
-    <t xml:space="preserve">Award cl 13.2 — shift supervisors where the majority of the shift falls outside 0830–1700. Nights are entered on the calculator page.</t>
+    <t xml:space="preserve">Award cl 13.2 — shift supervisors where the majority of the shift falls outside 0830–1700. Nights are entered on the calculator page. NOT IN THIS WORKBOOK: the $17.35 overtime meal allowance (Award cl 13.5) was added to the website calculator on 26.07.2026 but has no cell here — add it to the "other taxable earnings" line if you need it.</t>
   </si>
   <si>
     <t xml:space="preserve">C · QUALIFICATION ALLOWANCE  ($ per fortnight)</t>
@@ -900,7 +900,7 @@
     <t xml:space="preserve">Employer super rate</t>
   </si>
   <si>
-    <t xml:space="preserve">Superannuation (State Public Sector) Regulation 2023 s 12 — 12.75% of salary, defined as earnings for ordinary hours PLUS shift loadings PLUS payments made on paid leave. Overtime is out. Laundry IS in: on a real payslip (11–24 Jul 2026) the employer contribution came to exactly 12.75% of the full gross, laundry included. Since 01.07.2023 you receive the full 12.75% whether or not you make the member contribution.</t>
+    <t xml:space="preserve">Superannuation (State Public Sector) Regulation 2023 s 12 — 12.75% of salary, defined as earnings for ordinary hours PLUS shift loadings PLUS payments made on paid leave. Overtime is out. Laundry IS in: on a real payslip (11–24 Jul 2026) the employer contribution came to exactly 12.75% of the full gross, laundry included. The overtime meal allowance is out too — it rides on overtime, so it is not ordinary time earnings. Since 01.07.2023 you receive the full 12.75% whether or not you make the member contribution.</t>
   </si>
   <si>
     <t xml:space="preserve">Super contributions tax</t>
@@ -4118,7 +4118,7 @@
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
       <c r="J73" s="49" t="n">
-        <f aca="false">EmpSuperRate*($J$43+$J$48+$F$32*HDRate+$J$57-$J$54-CustomAllow)</f>
+        <f aca="false">EmpSuperRate*($J$43+$J$48+$F$32*HDRate+$J$57-CustomAllow)</f>
         <v>494.51930589024</v>
       </c>
     </row>
@@ -6511,7 +6511,7 @@
         <v>323</v>
       </c>
       <c r="I5" s="113" t="n">
-        <f aca="false">IF('Pay Calculator'!$C$14="No leave",0,N('Pay Calculator'!$B$14))</f>
+        <f aca="false">IF('Pay Calculator'!$C$14="No leave",0,IF(AND('Pay Calculator'!$B$5="Casual",OR('Pay Calculator'!$C$14="Sick / carer's",'Pay Calculator'!$C$14="Annual / recreation")),0,N('Pay Calculator'!$B$14)))</f>
         <v>0</v>
       </c>
     </row>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -2010,7 +2010,7 @@
     </xf>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -154,7 +154,7 @@
     <t xml:space="preserve">Shift class — higher duties</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto follows the HD level (Custom or None =&gt; 27.46%)</t>
+    <t xml:space="preserve">Auto follows the HD level: OO6 = 27.46%, everything else (Custom included) = 26.96%</t>
   </si>
   <si>
     <t xml:space="preserve">TSV location allowance</t>
@@ -585,7 +585,7 @@
     <t xml:space="preserve">Operational</t>
   </si>
   <si>
-    <t xml:space="preserve">$4.9867 per ordinary hour, capped at $379.00/fn — exactly 76 hours’ worth (EBA cl 2.10(3)). Recognises the operational nature of the role. Paid on annual, long service and special leave, but NOT sick leave (cl 2.10(4)–(5)).</t>
+    <t xml:space="preserve">$4.9867 per ordinary hour, capped at $379.00/fn — near enough to 76 hours’ worth ($378.99), so the cap only bites once leave or higher-duties hours push you past 76 (EBA cl 2.10(3)). Recognises the operational nature of the role. Paid on annual, long service and special leave, but NOT sick leave (cl 2.10(4)–(5)).</t>
   </si>
   <si>
     <t xml:space="preserve">Retention</t>
@@ -597,7 +597,7 @@
     <t xml:space="preserve">Laundry</t>
   </si>
   <si>
-    <t xml:space="preserve">$6.10/fn spread across ordinary hours (Award cl 13.6(b), CPI-adjusted each State Wage Case). Only for hours actually worked — no shifts, no washing, no allowance.</t>
+    <t xml:space="preserve">$6.10/fn spread across ordinary hours (Award cl 13.6(b)). It is an expense allowance, so it moves with CPI rather than with the State Wage Case (cl 13.7(b)). Only for hours actually worked — no shifts, no washing, no allowance.</t>
   </si>
   <si>
     <t xml:space="preserve">Qualification</t>
@@ -615,7 +615,7 @@
     <t xml:space="preserve">Other taxable earnings</t>
   </si>
   <si>
-    <t xml:space="preserve">A flexible taxable line for anything not covered above — most commonly a secondee travel/meal allowance for Brisbane staff working in TSV, but usable for any taxable one-off. You type the amount (on the calculator, on the In-charge row). It is added to gross and taxed as wages, but excluded from the super base (it is not ordinary-time earnings). If your payment is instead a genuine tax-free reimbursement, leave this blank and use the custom pre-tax deduction.</t>
+    <t xml:space="preserve">A flexible taxable line for anything not covered above — most commonly a secondee travel/meal allowance for Brisbane staff working in TSV, but usable for any taxable one-off. You type the amount (on the calculator, on the In-charge row). It is added to gross and taxed as wages, but excluded from the super base (it is not ordinary-time earnings). If your payment is instead a genuine tax-free reimbursement, it does not belong anywhere in this workbook — leave it out entirely.</t>
   </si>
   <si>
     <t xml:space="preserve">③   PENALTIES &amp; EXTRAS</t>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="I50" s="8"/>
       <c r="J50" s="49" t="n">
-        <f aca="false">($B$32*BaseRate+LeavePay*LvShift)*$G$50+$F$32*HDRate*IF($B$9="None",0,IF($B$9="OO3-OO5 (26.96%)",Rate_ShiftLo,IF($B$9="OO6 (27.46%)",Rate_ShiftHi,IF(LEFT($B$7,2)="L5",Rate_ShiftLo,Rate_ShiftHi))))</f>
+        <f aca="false">($B$32*BaseRate+LeavePay*LvShift)*$G$50+$F$32*HDRate*IF($B$9="None",0,IF($B$9="OO3-OO5 (26.96%)",Rate_ShiftLo,IF($B$9="OO6 (27.46%)",Rate_ShiftHi,IF(LEFT($B$7,2)="L6",Rate_ShiftHi,Rate_ShiftLo))))</f>
         <v>733.584231296</v>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       <c r="E51" s="51"/>
       <c r="F51" s="51"/>
       <c r="G51" s="57" t="n">
-        <f aca="false">IF($B$10="Full rate",Rate_TSVFull,IF($B$10="Half rate",Rate_TSVHalf,0))</f>
+        <f aca="false">IF($B$5="Casual",0,IF($B$10="Full rate",Rate_TSVFull,IF($B$10="Half rate",Rate_TSVHalf,0)))</f>
         <v>0</v>
       </c>
       <c r="H51" s="52" t="s">

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -699,10 +699,10 @@
     <t xml:space="preserve">ATO Schedule 8 — nothing withheld until taxable pay reaches about $2,674/fn (threshold claimed), then a marginal slice on top. Heads-up: salary sacrificing lowers the fortnightly STSL withheld but NOT the annual repayment (repayment income adds sacrificed super back), so heavy sacrificing with a HELP debt can mean a tax-time catch-up.</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary sacrifice &amp; gross-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concessional super is taxed 15% inside the fund, so a straight 5% sacrifice only lands 4.25%. Grossing up means sending 5% ÷ 0.85 = 5.88% so the full 5% still lands — and because it left your pay before income tax, you still bank roughly $50/fn more than paying it after tax.</t>
+    <t xml:space="preserve">Salary sacrifice — no gross-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacrificed super is taxed 15% inside the fund, so a 5% sacrifice only lands 4.25%. Payroll does NOT top that up for you — a payslip we checked deducted exactly 5.00% of the fortnightly salary, not 5.88%. If you want a full 5% to land, set the member rate to 5.88% yourself (5 ÷ 0.85). Sacrificing is still ahead of paying it after tax, because it leaves your pay before income tax does.</t>
   </si>
   <si>
     <t xml:space="preserve">Employer contributions + everything salary-sacrificed count toward $32,500/yr (FY2026-27). After-tax member contributions don’t. The super section tracks your headroom automatically.</t>
@@ -906,7 +906,7 @@
     <t xml:space="preserve">Super contributions tax</t>
   </si>
   <si>
-    <t xml:space="preserve">Tax the fund deducts from employer and salary-sacrificed (concessional) contributions. After-tax member contributions are NOT taxed in the fund — which is why sacrificing the standard 5% needs a gross-up to land the same amount. Study-loan heads-up: sacrificing lowers fortnightly STSL withholding but NOT the annual repayment (repayment income adds sacrificed super back), so expect a small tax-time catch-up if you sacrifice while holding a HELP debt.</t>
+    <t xml:space="preserve">Tax the fund deducts from employer and salary-sacrificed (concessional) contributions. After-tax member contributions are NOT taxed in the fund. Payroll does not gross up a sacrificed contribution, so a 5% sacrifice lands 4.25% — set the rate to 5.88% yourself if you want a full 5% in. Study-loan heads-up: sacrificing lowers fortnightly STSL withholding but NOT the annual repayment (repayment income adds sacrificed super back), so expect a small tax-time catch-up if you sacrifice while holding a HELP debt.</t>
   </si>
   <si>
     <t xml:space="preserve">SG minimum rate</t>
@@ -3921,12 +3921,12 @@
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
       <c r="H62" s="8" t="str">
-        <f aca="false">IF($E$62="No — after-tax","Remserv can take your standard 5% pre-tax instead — grossed up so the full 5% still lands",TEXT($E$69/(1-ContribTax),"0.00%")&amp;" of base, pre-tax — lands the full "&amp;TEXT($E$69,"0%")&amp;" after the fund's 15% tax")</f>
-        <v>Remserv can take your standard 5% pre-tax instead — grossed up so the full 5% still lands</v>
+        <f aca="false">IF($E$62="No — after-tax","Remserv can take your standard 5% pre-tax instead — the same percentage, but it leaves before income tax",TEXT($E$69,"0.00%")&amp;" of base, pre-tax — the fund's 15% tax then leaves "&amp;TEXT($E$69*(1-ContribTax),"0.00%")&amp;" in your account")</f>
+        <v>Remserv can take your standard 5% pre-tax instead — the same percentage, but it leaves before income tax</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="49" t="n">
-        <f aca="false">IF($E$62="No — after-tax",0,$E$69*($J$43+$F$32*HDRate)/(1-ContribTax))</f>
+        <f aca="false">IF($E$62="No — after-tax",0,$E$69*($J$43+$F$32*HDRate))</f>
         <v>0</v>
       </c>
     </row>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -3632,7 +3632,7 @@
       <c r="C47" s="48"/>
       <c r="D47" s="48"/>
       <c r="F47" s="8" t="str">
-        <f aca="false">TEXT(SUM($F$32:$I$32),"0.0")&amp;" hrs @ HD rates"</f>
+        <f aca="false">IF(AND(SUM($F$32:$I$32)&gt;0,OR($B$7="None",AND(OR($B$7="Custom",$B$7=""),N($D$7)=0))),TEXT(SUM($F$32:$I$32),"0.0")&amp;" hrs @ base — no HD level/rate picked",TEXT(SUM($F$32:$I$32),"0.0")&amp;" hrs @ HD rates")</f>
         <v>0.0 hrs @ HD rates</v>
       </c>
       <c r="G47" s="8"/>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="I50" s="8"/>
       <c r="J50" s="49" t="n">
-        <f aca="false">($B$32*BaseRate+LeavePay*LvShift)*$G$50+$F$32*HDRate*IF($B$9="None",0,IF($B$9="OO3-OO5 (26.96%)",Rate_ShiftLo,IF($B$9="OO6 (27.46%)",Rate_ShiftHi,IF(LEFT($B$7,2)="L6",Rate_ShiftHi,Rate_ShiftLo))))</f>
+        <f aca="false">($B$32*BaseRate+LeavePay*LvShift)*$G$50+$F$32*HDRate*IF(OR($B$7="None",AND(OR($B$7="Custom",$B$7=""),N($D$7)=0)),$G$50,IF($B$9="None",0,IF($B$9="OO3-OO5 (26.96%)",Rate_ShiftLo,IF($B$9="OO6 (27.46%)",Rate_ShiftHi,IF(LEFT($B$7,2)="L6",Rate_ShiftHi,Rate_ShiftLo)))))</f>
         <v>733.584231296</v>
       </c>
     </row>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I51" s="52"/>
       <c r="J51" s="53" t="n">
-        <f aca="false">MIN($B$32+$F$32+LeaveHrs,76)*$G$51</f>
+        <f aca="false">MIN($B$32+$F$32+LeaveHrs+$D$32,76)*$G$51</f>
         <v>0</v>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="I52" s="8"/>
       <c r="J52" s="49" t="n">
-        <f aca="false">MIN($B$32+$F$32+LeaveHrs*LvOper,76)*$G$52</f>
+        <f aca="false">MIN($B$32+$F$32+LeaveHrs*LvOper+$D$32,76)*$G$52</f>
         <v>378.9892</v>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="I53" s="52"/>
       <c r="J53" s="53" t="n">
-        <f aca="false">MIN($B$32+$F$32+LeaveHrs*LvRet,76)*$G$53</f>
+        <f aca="false">MIN($B$32+$F$32+LeaveHrs*LvRet+$D$32,76)*$G$53</f>
         <v>44.9996</v>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="49" t="n">
-        <f aca="false">MIN($B$32+$F$32,76)*$G$54</f>
+        <f aca="false">MIN($B$32+$F$32+$D$32,76)*$G$54</f>
         <v>6.099988</v>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="49" t="n">
-        <f aca="false">IF($E$62="No — after-tax",0,$E$69*($J$43+$F$32*HDRate))</f>
+        <f aca="false">IF($E$62="No — after-tax",0,$E$69*($J$43+$F$32*HDRate+$D$32*BaseRate))</f>
         <v>0</v>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
       <c r="J69" s="49" t="n">
-        <f aca="false">IF($E$62="No — after-tax",$E$69*($J$43+$F$32*HDRate),0)</f>
+        <f aca="false">IF($E$62="No — after-tax",$E$69*($J$43+$F$32*HDRate+$D$32*BaseRate),0)</f>
         <v>136.050488</v>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
       <c r="J73" s="49" t="n">
-        <f aca="false">EmpSuperRate*($J$43+$J$48+$F$32*HDRate+$J$57-CustomAllow)</f>
+        <f aca="false">EmpSuperRate*($J$43+$J$45+$J$48+$F$32*HDRate+$J$57-CustomAllow)</f>
         <v>494.51930589024</v>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Yes runs your 5% member super through pre-tax pay (Remserv), grossed up so the full 5% still lands after the fund's 15% tax. More take-home, same super." promptTitle="Package the standard 5%?" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="E62" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Yes runs your member % through pre-tax pay (Remserv). Payroll does not gross it up — the full typed percentage is what lands. If you were quoted a grossed-up figure like 5.88 (5 ÷ 0.85), type that instead. More take-home, same super." promptTitle="Package the standard 5%?" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="E62" type="list">
       <formula1>"No — after-tax,Yes — pre-tax"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6527,7 +6527,7 @@
         <v>325</v>
       </c>
       <c r="F6" s="112" t="n">
-        <f aca="false">IF('Pay Calculator'!$B$7="None",0,IF(OR('Pay Calculator'!$B$7="Custom",'Pay Calculator'!$B$7=""),N('Pay Calculator'!$D$7),IFERROR(INDEX(PayScaleRates,MATCH('Pay Calculator'!$B$7,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$7))))</f>
+        <f aca="false">IF('Pay Calculator'!$B$7="None",F5,IF(OR('Pay Calculator'!$B$7="Custom",'Pay Calculator'!$B$7=""),IF(N('Pay Calculator'!$D$7)&gt;0,N('Pay Calculator'!$D$7),F5),IFERROR(INDEX(PayScaleRates,MATCH('Pay Calculator'!$B$7,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$7))))</f>
         <v>41.78947</v>
       </c>
       <c r="H6" s="111" t="s">

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -870,7 +870,7 @@
     <t xml:space="preserve">$ / night</t>
   </si>
   <si>
-    <t xml:space="preserve">Award cl 13.2 — shift supervisors where the majority of the shift falls outside 0830–1700. Nights are entered on the calculator page. NOT IN THIS WORKBOOK: the $17.35 overtime meal allowance (Award cl 13.5) was added to the website calculator on 26.07.2026 but has no cell here — add it to the "other taxable earnings" line if you need it.</t>
+    <t xml:space="preserve">Award cl 13.2 — shift supervisors where the majority of the shift falls outside 0830–1700. Nights are entered on the calculator page.</t>
   </si>
   <si>
     <t xml:space="preserve">C · QUALIFICATION ALLOWANCE  ($ per fortnight)</t>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -75,6 +75,8 @@
     <definedName function="false" hidden="false" name="MemberPct" vbProcedure="false">'Pay Calculator'!$E$69</definedName>
     <definedName function="false" hidden="false" name="NetBank" vbProcedure="false">'Pay Calculator'!$F$35</definedName>
     <definedName function="false" hidden="false" name="PAYG_FN" vbProcedure="false">'Tax Engine'!$F$15</definedName>
+    <definedName function="false" hidden="false" name="QScaleNames" vbProcedure="false">'Settings &amp; Rates'!$A$70:$A$73</definedName>
+    <definedName function="false" hidden="false" name="QScaleRates" vbProcedure="false">'Settings &amp; Rates'!$B$70:$C$73</definedName>
     <definedName function="false" hidden="false" name="PayScaleAll" vbProcedure="false">'Settings &amp; Rates'!$A$6:$D$20</definedName>
     <definedName function="false" hidden="false" name="PayScaleNames" vbProcedure="false">'Settings &amp; Rates'!$A$6:$A$20</definedName>
     <definedName function="false" hidden="false" name="PayScaleRates" vbProcedure="false">'Settings &amp; Rates'!$B$6:$C$20</definedName>
@@ -104,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="439">
   <si>
     <t xml:space="preserve">PAY  CALCULATOR</t>
   </si>
@@ -603,7 +605,7 @@
     <t xml:space="preserve">Qualification</t>
   </si>
   <si>
-    <t xml:space="preserve">Flat fortnightly amount for holding the qual once you’re at the top paypoint of your level for 12 months (EBA cl 4.2): Cert IV $41.50 (OO3) · Diploma $42.80 (OO4/OO5) · Adv Diploma $44.60 (OO6).</t>
+    <t xml:space="preserve">Worth $41.50 (OO3) · $42.80 (OO4/OO5) · $44.60 (OO6) a fortnight (EBA cl 4.2), once you have held the top paypoint of your level for 12 months. Casuals take longer: a calendar year AND 1,200 hours at the top paypoint (cl 4.1(c)). There is no separate setting for it — payroll folds it into your rate and stores the result as one classification, so pick L3-Q, L4-Q, L5-Q or L6-Q in the Classification box. Inside the rate it is pro-rated by the hours you work, picks up the casual 25% loading and counts toward the shift allowance, which is worth a little more than being paid flat.</t>
   </si>
   <si>
     <t xml:space="preserve">In-charge</t>
@@ -1414,6 +1416,21 @@
   </si>
   <si>
     <t xml:space="preserve">Scales 8-10, Actors, FS and the constants above are carried for reference — the calculator itself uses scales 1/2/3/5/6 plus the two study-loan tables.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now part of your classification. Payroll folds the EBA cl 4.2 allowance into the rate instead of paying it as its own line, so pick L3-Q, L4-Q, L5-Q or L6-Q in the Classification box above. There is no separate setting any more.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualification (inside the rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F · QUALIFIED PAYPOINTS — the "Q" classifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q means qualified. Payroll adds the EBA cl 4.2 qualification allowance to the top paypoint of your level and stores the result as one classification (YDZO3Q, 4Q, 5Q), so these are chosen in the Classification box rather than set separately. The allowance is only ever payable at a level’s top paypoint, so these four cover everyone entitled to it. Each rate is built live from the award salary above plus the allowance in block C — change either and these follow. Only L3-Q has been seen on a payslip; the other three are the same arithmetic on their level’s top paypoint.</t>
   </si>
 </sst>
 </file>
@@ -3025,14 +3042,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>18</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="8" t="s">
-        <v>24</v>
+        <v>435</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
@@ -3781,7 +3796,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="50" t="s">
-        <v>23</v>
+        <v>436</v>
       </c>
       <c r="B55" s="50"/>
       <c r="C55" s="50"/>
@@ -3789,7 +3804,7 @@
       <c r="E55" s="51"/>
       <c r="F55" s="51"/>
       <c r="G55" s="59" t="n">
-        <f aca="false">VLOOKUP($B$12,QualTable,2,FALSE())</f>
+        <f aca="false">0</f>
         <v>0</v>
       </c>
       <c r="H55" s="52" t="s">
@@ -4737,13 +4752,13 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="19">
+  <dataValidations count="18">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Sets the rate column (casual = +25%) and the auto rules: casuals get no TSV allowance and 0% member super." promptTitle="Employment type" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B5" type="list">
       <formula1>"Permanent,Casual"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Pick your level and paypoint. Pick Custom to type your own hourly rate in the teal box to the right." promptTitle="Classification" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B6" type="list">
-      <formula1>"Custom,L3-1,L3-2,L3-3,L3-4,L4-1,L4-2,L4-3,L4-4,L5-1,L5-2,L5-3,L5-4,L6-1,L6-2,L6-3"</formula1>
+      <formula1>"L3-1,L3-2,L3-3,L3-4,L3-Q,L4-1,L4-2,L4-3,L4-4,L4-Q,L5-1,L5-2,L5-3,L5-4,L5-Q,L6-1,L6-2,L6-3,L6-Q,Custom"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Only if you acted up this fortnight. HD hours go in columns F-I of the timesheet. None = not acting." promptTitle="Higher duties" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B7" type="list">
@@ -4776,10 +4791,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Yes after 2 years' continuous service (EBA cl 2.12). $45/fn pro-rata on ordinary hours." promptTitle="Retention allowance" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B11" type="list">
       <formula1>"Yes,No"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B12" type="list">
-      <formula1>"None,Cert IV,Diploma,Adv Diploma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Nights you were in charge of shift (OPS1 on nights). $15.65 per night, award cl 13.2." promptTitle="In-charge nights" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B13" type="list">
@@ -5626,7 +5637,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
@@ -6408,15 +6419,121 @@
         <v>317</v>
       </c>
     </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="90" t="s">
+        <v>437</v>
+      </c>
+      <c r="B68" s="90"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="90"/>
+      <c r="E68" s="90"/>
+      <c r="F68" s="90"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="93" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="94" t="s">
+        <v>215</v>
+      </c>
+      <c r="C69" s="94" t="s">
+        <v>216</v>
+      </c>
+      <c r="D69" s="94" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="95" t="inlineStr">
+        <is>
+          <t>L3-Q</t>
+        </is>
+      </c>
+      <c r="B70" s="96">
+        <f aca="false">(ROUND(D9,0)+$B$36)/76</f>
+        <v>36.34868421052632</v>
+      </c>
+      <c r="C70" s="97">
+        <f aca="false">B70*1.25</f>
+        <v>45.4358552631579</v>
+      </c>
+      <c r="D70" s="98">
+        <f aca="false">B70*76</f>
+        <v>2762.5</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="95" t="inlineStr">
+        <is>
+          <t>L4-Q</t>
+        </is>
+      </c>
+      <c r="B71" s="96">
+        <f aca="false">(ROUND(D13,0)+$B$37)/76</f>
+        <v>41.32631578947368</v>
+      </c>
+      <c r="C71" s="97">
+        <f aca="false">B71*1.25</f>
+        <v>51.65789473684211</v>
+      </c>
+      <c r="D71" s="98">
+        <f aca="false">B71*76</f>
+        <v>3140.8</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="95" t="inlineStr">
+        <is>
+          <t>L5-Q</t>
+        </is>
+      </c>
+      <c r="B72" s="96">
+        <f aca="false">(ROUND(D17,0)+$B$37)/76</f>
+        <v>46.3921052631579</v>
+      </c>
+      <c r="C72" s="97">
+        <f aca="false">B72*1.25</f>
+        <v>57.99013157894737</v>
+      </c>
+      <c r="D72" s="98">
+        <f aca="false">B72*76</f>
+        <v>3525.8</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="95" t="inlineStr">
+        <is>
+          <t>L6-Q</t>
+        </is>
+      </c>
+      <c r="B73" s="96">
+        <f aca="false">(ROUND(D20,0)+$B$38)/76</f>
+        <v>50.81052631578947</v>
+      </c>
+      <c r="C73" s="97">
+        <f aca="false">B73*1.25</f>
+        <v>63.51315789473684</v>
+      </c>
+      <c r="D73" s="98">
+        <f aca="false">B73*76</f>
+        <v>3861.6</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="99" t="s">
+        <v>438</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection sheet="true" password="ec70" formatCells="false" sort="false" autoFilter="false"/>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A68:F68"/>
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B53:D53"/>
@@ -6504,7 +6621,7 @@
         <v>322</v>
       </c>
       <c r="F5" s="112" t="n">
-        <f aca="false">IF(OR('Pay Calculator'!$B$6="Custom",'Pay Calculator'!$B$6=""),N('Pay Calculator'!$D$6),IFERROR(INDEX(PayScaleRates,MATCH('Pay Calculator'!$B$6,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$6)))</f>
+        <f aca="false">IF(OR('Pay Calculator'!$B$6="Custom",'Pay Calculator'!$B$6=""),N('Pay Calculator'!$D$6),IFERROR(INDEX(QScaleRates,MATCH('Pay Calculator'!$B$6,QScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),IFERROR(INDEX(PayScaleRates,MATCH('Pay Calculator'!$B$6,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$6))))</f>
         <v>35.80263</v>
       </c>
       <c r="H5" s="111" t="s">

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -3040,7 +3040,7 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
         <v>434</v>
       </c>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -25,6 +25,7 @@
     <definedName function="false" hidden="false" name="EmpSuperRate" vbProcedure="false">'Settings &amp; Rates'!$B$41</definedName>
     <definedName function="false" hidden="false" name="FeeDefault" vbProcedure="false">'Settings &amp; Rates'!$B$46</definedName>
     <definedName function="false" hidden="false" name="FnPerYear" vbProcedure="false">'Settings &amp; Rates'!$B$47</definedName>
+    <definedName function="false" hidden="false" name="HDCode" vbProcedure="false">'Settings &amp; Rates'!$B$76</definedName>
     <definedName function="false" hidden="false" name="HDRate" vbProcedure="false">'Tax Engine'!$F$6</definedName>
     <definedName function="false" hidden="false" name="Hrs_PHRDO" vbProcedure="false">'Settings &amp; Rates'!$B$48</definedName>
     <definedName function="false" hidden="false" name="LeaveHrs" vbProcedure="false">'Tax Engine'!$I$5</definedName>
@@ -2952,10 +2953,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C7" s="10" t="n">
-        <f aca="false">IF(OR($B$7="None",$B$7="Custom",$B$7=""),"",IFERROR(INDEX(PayScaleRates,MATCH($B$7,PayScaleNames,0),IF($B$5="Casual",2,1)),""))</f>
+        <f aca="false">IF(OR(HDCode="None",HDCode="Custom",HDCode=""),"",IFERROR(INDEX(PayScaleRates,MATCH(HDCode,PayScaleNames,0),IF($B$5="Casual",2,1)),""))</f>
         <v>41.78947</v>
       </c>
       <c r="D7" s="11"/>
@@ -3647,7 +3648,7 @@
       <c r="C47" s="48"/>
       <c r="D47" s="48"/>
       <c r="F47" s="8" t="str">
-        <f aca="false">IF(AND(SUM($F$32:$I$32)&gt;0,OR($B$7="None",AND(OR($B$7="Custom",$B$7=""),N($D$7)=0))),TEXT(SUM($F$32:$I$32),"0.0")&amp;" hrs @ base — no HD level/rate picked",TEXT(SUM($F$32:$I$32),"0.0")&amp;" hrs @ HD rates")</f>
+        <f aca="false">IF(AND(SUM($F$32:$I$32)&gt;0,OR(HDCode="None",AND(OR(HDCode="Custom",HDCode=""),N($D$7)=0))),TEXT(SUM($F$32:$I$32),"0.0")&amp;" hrs @ base — no HD level/rate picked",TEXT(SUM($F$32:$I$32),"0.0")&amp;" hrs @ HD rates")</f>
         <v>0.0 hrs @ HD rates</v>
       </c>
       <c r="G47" s="8"/>
@@ -3706,7 +3707,7 @@
       </c>
       <c r="I50" s="8"/>
       <c r="J50" s="49" t="n">
-        <f aca="false">($B$32*BaseRate+LeavePay*LvShift)*$G$50+$F$32*HDRate*IF(OR($B$7="None",AND(OR($B$7="Custom",$B$7=""),N($D$7)=0)),$G$50,IF($B$9="None",0,IF($B$9="OO3-OO5 (26.96%)",Rate_ShiftLo,IF($B$9="OO6 (27.46%)",Rate_ShiftHi,IF(LEFT($B$7,2)="L6",Rate_ShiftHi,Rate_ShiftLo)))))</f>
+        <f aca="false">($B$32*BaseRate+LeavePay*LvShift)*$G$50+$F$32*HDRate*IF(OR(HDCode="None",AND(OR(HDCode="Custom",HDCode=""),N($D$7)=0)),$G$50,IF($B$9="None",0,IF($B$9="OO3-OO5 (26.96%)",Rate_ShiftLo,IF($B$9="OO6 (27.46%)",Rate_ShiftHi,IF(LEFT(HDCode,2)="L6",Rate_ShiftHi,Rate_ShiftLo)))))</f>
         <v>733.584231296</v>
       </c>
     </row>
@@ -4761,8 +4762,8 @@
       <formula1>"L3-1,L3-2,L3-3,L3-4,L3-Q,L4-1,L4-2,L4-3,L4-4,L4-Q,L5-1,L5-2,L5-3,L5-4,L5-Q,L6-1,L6-2,L6-3,L6-Q,Custom"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Only if you acted up this fortnight. HD hours go in columns F-I of the timesheet. None = not acting." promptTitle="Higher duties" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B7" type="list">
-      <formula1>"None,Custom,L5-1,L5-2,L5-3,L5-4,L6-1,L6-2,L6-3"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Auto follows your classification: L3/L4 act into L5-1, L5 into L6-1 (award cl 12.7). Pick a level or None to override. HD hours go in columns F-I of the timesheet." promptTitle="Higher duties" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B7" type="list">
+      <formula1>"Auto,None,Custom,L5-1,L5-2,L5-3,L5-4,L6-1,L6-2,L6-3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B8" type="list">
@@ -5637,7 +5638,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
@@ -6522,6 +6523,17 @@
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="99" t="s">
         <v>438</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="95" t="inlineStr">
+        <is>
+          <t>Effective higher-duties code — resolves the Auto option from the classification. The engine reads this cell, not B7 on Pay Calculator.</t>
+        </is>
+      </c>
+      <c r="B76" t="str">
+        <f aca="false">IF('Pay Calculator'!$B$7&lt;&gt;"Auto",'Pay Calculator'!$B$7,IF(OR(LEFT('Pay Calculator'!$B$6,2)="L3",LEFT('Pay Calculator'!$B$6,2)="L4"),"L5-1",IF(LEFT('Pay Calculator'!$B$6,2)="L5","L6-1","None")))</f>
+        <v>L5-1</v>
       </c>
     </row>
   </sheetData>
@@ -6644,7 +6656,7 @@
         <v>325</v>
       </c>
       <c r="F6" s="112" t="n">
-        <f aca="false">IF('Pay Calculator'!$B$7="None",F5,IF(OR('Pay Calculator'!$B$7="Custom",'Pay Calculator'!$B$7=""),IF(N('Pay Calculator'!$D$7)&gt;0,N('Pay Calculator'!$D$7),F5),IFERROR(INDEX(PayScaleRates,MATCH('Pay Calculator'!$B$7,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$7))))</f>
+        <f aca="false">IF(HDCode="None",F5,IF(OR(HDCode="Custom",HDCode=""),IF(N('Pay Calculator'!$D$7)&gt;0,N('Pay Calculator'!$D$7),F5),IFERROR(INDEX(PayScaleRates,MATCH(HDCode,PayScaleNames,0),IF('Pay Calculator'!$B$5="Casual",2,1)),N('Pay Calculator'!$D$7))))</f>
         <v>41.78947</v>
       </c>
       <c r="H6" s="111" t="s">

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -142,7 +142,7 @@
     <t xml:space="preserve">L5-1</t>
   </si>
   <si>
-    <t xml:space="preserve">← custom HD rate goes in the teal box · None = not acting</t>
+    <t xml:space="preserve">← custom HD rate goes in the teal box · Auto follows your classification (L3/L4 → L5-1, L5 → L6-1) · None = not acting</t>
   </si>
   <si>
     <t xml:space="preserve">Shift allowance class</t>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -429,7 +429,7 @@
     <t xml:space="preserve">Standard member super</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom post-tax deduction</t>
+    <t>Post-tax deduction 1</t>
   </si>
   <si>
     <t xml:space="preserve">e.g. novated lease post-tax leg</t>
@@ -3484,7 +3484,7 @@
       <c r="D35" s="40"/>
       <c r="E35" s="40"/>
       <c r="F35" s="41" t="n">
-        <f aca="false">$J$66-$J$67-$J$68-$J$69-$J$70</f>
+        <f aca="false">$J$66-$J$67-$J$68-$J$69-$J$70-$J$71</f>
         <v>2868.632291296</v>
       </c>
       <c r="G35" s="41"/>
@@ -4104,7 +4104,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="50" t="inlineStr">
+        <is>
+          <t>Post-tax deduction 2</t>
+        </is>
+      </c>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="52" t="inlineStr">
+        <is>
+          <t>e.g. bank or credit-union deduction</t>
+        </is>
+      </c>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
+      <c r="J71" s="53" t="n">
+        <f aca="false">$E$71</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>106</v>
@@ -4400,7 +4424,7 @@
       <c r="H89" s="51"/>
       <c r="I89" s="51"/>
       <c r="J89" s="80" t="n">
-        <f aca="false">$J$64+$J$65+$J$70</f>
+        <f aca="false">$J$64+$J$65+$J$70+$J$71</f>
         <v>0</v>
       </c>
     </row>
@@ -4562,7 +4586,7 @@
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="ec70" formatCells="false" sort="false" autoFilter="false"/>
-  <mergeCells count="143">
+  <mergeCells count="145">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
@@ -4651,7 +4675,9 @@
     <mergeCell ref="A69:D69"/>
     <mergeCell ref="F69:I69"/>
     <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
     <mergeCell ref="F70:I70"/>
+    <mergeCell ref="F71:I71"/>
     <mergeCell ref="A72:J72"/>
     <mergeCell ref="A73:D73"/>
     <mergeCell ref="F73:I73"/>

--- a/PayCalc_V19.xlsx
+++ b/PayCalc_V19.xlsx
@@ -196,7 +196,7 @@
     <t xml:space="preserve">No leave</t>
   </si>
   <si>
-    <t xml:space="preserve">hours + type · sick/carer's = base + retention only; annual &amp; long service also carry shift and operational (EBA cl 2.9(5), 2.10(5), 2.12)</t>
+    <t xml:space="preserve">hours + type · pays base rate; which allowances keep paying depends on the leave type — the Pay Guide tab has the full breakdown</t>
   </si>
   <si>
     <t xml:space="preserve">▸ Public holidays on your RDO</t>
@@ -408,13 +408,13 @@
     <t xml:space="preserve">Custom pre-tax deduction</t>
   </si>
   <si>
-    <t xml:space="preserve">e.g. novated lease</t>
+    <t xml:space="preserve">e.g. novated lease pre-tax leg</t>
   </si>
   <si>
     <t xml:space="preserve">Salary-packaging admin fee</t>
   </si>
   <si>
-    <t xml:space="preserve">Remserv ≈ $1.35 if applicable</t>
+    <t xml:space="preserve">e.g. RemServ — the fee varies, take it off your payslip</t>
   </si>
   <si>
     <t xml:space="preserve">TAXABLE INCOME</t>
@@ -426,7 +426,7 @@
     <t xml:space="preserve">Study-loan repayment (STSL)</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard member super</t>
+    <t xml:space="preserve">Member contribution rate</t>
   </si>
   <si>
     <t>Post-tax deduction 1</t>
@@ -654,7 +654,7 @@
     <t xml:space="preserve">Minimum engagements</t>
   </si>
   <si>
-    <t xml:space="preserve">Casual and part-time engagements carry a 2-hour minimum, recall to duty 2 hours, overtime on a day off 3 hours (Award cl 8, 18). The calculator takes raw hours — enter the minimum, not the shorter time worked.</t>
+    <t xml:space="preserve">Casual and part-time engagements carry a 2-hour minimum (Award cl 8.2(c), 8.3(d)); recall to duty pays a 2-hour minimum at overtime rates (cl 18.4). Ordinary overtime has no minimum — double time for the hours you actually work (cl 18.3). The calculator takes raw hours — enter the minimum, not the shorter time worked.</t>
   </si>
   <si>
     <t xml:space="preserve">④   LEAVE — WHAT YOU KEEP, WHAT STOPS</t>
@@ -663,13 +663,13 @@
     <t xml:space="preserve">Annual &amp; long service</t>
   </si>
   <si>
-    <t xml:space="preserve">Base rate for your rostered hours — continuous shift workers accrue five weeks’ rec leave a year (the 5th week is the Queensland Employment Standards shiftworker entitlement). KEEPS: shift allowance through both rec leave AND long service leave — paid in lieu of the award’s leave loading (EBA cl 2.9(5)), and at 26.96–27.46% it’s worth more than the loading it replaces. Also keeps operational (cl 2.10(5)), retention (cl 2.12) and TSV (Directive 16/18). DOESN’T GET: laundry or in-charge — those only exist for shifts actually worked, and no separate 17.5% loading on top. A leave fortnight lands within a few dollars of a worked one.</t>
+    <t xml:space="preserve">Base rate for your rostered hours — continuous shift workers accrue five weeks’ rec leave a year (20 days plus an extra week for continuous shift workers — Dir 11/24 Sch 1 cl 2.1; 25 days outright in the Northern/Western region). KEEPS: shift allowance through both rec leave AND long service leave — paid in lieu of the award’s leave loading (EBA cl 2.9(5)), and at 26.96–27.46% it’s worth more than the loading it replaces. Also keeps operational (cl 2.10(5)), retention (cl 2.12) and TSV (Directive 16/18). DOESN’T GET: laundry or in-charge — those only exist for shifts actually worked, and no separate 17.5% loading on top. A leave fortnight lands within a few dollars of a worked one.</t>
   </si>
   <si>
     <t xml:space="preserve">Leave loading — who gets it</t>
   </si>
   <si>
-    <t xml:space="preserve">Continuous shift workers (this whole roster) DON’T get the separate annual leave loading — the CSA continuing through leave IS the loading, and it pays better. Day workers at the centre are the ones on classic loading: 17.5% on four weeks’ accrual, or 14% across all five at the employer’s discretion (EBA cl 2.13); where paid, it’s consolidated into a December payment (cl 2.4). The calculator doesn’t model day-worker loading — it’s built for the shift roster.</t>
+    <t xml:space="preserve">You don’t get a separate leave loading, and you’re not missing out — the shift allowance keeps running through recreation and long service leave INSTEAD of one (EBA cl 2.9(5)), and at 26.96–27.46% it comes to more than a loading would. That’s what this workbook pays. A pay summary in July 2026 settled it: the element is named “Consolidated Allow 26.96% WrkRec”, with no separate loading line of any kind.</t>
   </si>
   <si>
     <t xml:space="preserve">Sick / carer’s</t>
@@ -711,13 +711,13 @@
     <t xml:space="preserve">Employer contributions + everything salary-sacrificed count toward $32,500/yr (FY2026-27). After-tax member contributions don’t. The super section tracks your headroom automatically.</t>
   </si>
   <si>
-    <t xml:space="preserve">12.75% of ordinary-time earnings — ordinary hours, shift allowance, ordinary-time allowances and paid leave all included; overtime excluded (Superannuation (State Public Sector) Regulation 2023). Paid whether or not you make the member contribution.</t>
+    <t xml:space="preserve">12.75% of ordinary-time earnings — ordinary hours, shift allowance, ordinary-time allowances (laundry included), paid leave and public holidays you work; overtime excluded (Superannuation (State Public Sector) Regulation 2023). Paid whether or not you make the member contribution.</t>
   </si>
   <si>
     <t xml:space="preserve">Member 5%</t>
   </si>
   <si>
-    <t xml:space="preserve">The standard employee contribution for permanents — after-tax by default, or packaged pre-tax through Remserv. Casuals default to 0%.</t>
+    <t xml:space="preserve">The standard employee contribution for permanents — after-tax by default, or packaged pre-tax through RemServ. Casuals default to 0%.</t>
   </si>
   <si>
     <t xml:space="preserve">⑥   GOOD TO KNOW</t>
@@ -930,10 +930,10 @@
     <t xml:space="preserve">Default after-tax member rate for permanent staff. Casuals default to 0% on the calculator.</t>
   </si>
   <si>
-    <t xml:space="preserve">Remserv admin fee (typical)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only relevant if salary packaging through Remserv.</t>
+    <t xml:space="preserve">Salary-packaging admin fee (typical)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only relevant if salary packaging through a provider (e.g. RemServ).</t>
   </si>
   <si>
     <t xml:space="preserve">Fortnights per year</t>
@@ -981,7 +981,7 @@
     <t xml:space="preserve">EBA CB/2023/139</t>
   </si>
   <si>
-    <t xml:space="preserve">Youth Detention Centre Certified Agreement 2023 — cl 2.9(4) shift, cl 2.10 operational, cl 2.12 retention, cl 4.2 qualification. Nominal expiry 31.07.2026.</t>
+    <t xml:space="preserve">Youth Detention Centre Certified Agreement 2023 — cl 2.9(4) shift, cl 2.10 operational, cl 2.12 retention, cl 4.2 qualification. Nominal expiry 31.07.2026 — passed; the agreement keeps operating until replaced.</t>
   </si>
   <si>
     <t xml:space="preserve">In-charge / laundry</t>
@@ -1023,10 +1023,10 @@
     <t xml:space="preserve">New certified agreement (YDC 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">OFFER 16.07.2026 — not yet certified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Offer dated 16.07.2026 (3-year term, expires 31.07.2029). Three increases: 1 Aug 2026 = 3.5% (3% + 0.5% CPI uplift, already triggered), 1 Aug 2027 = 2.5%, 1 Aug 2028 = 2.5%. The FIRST rise applies to the higher of Award or Agreement — i.e. the Award rate (cl 2.18(6) retained). Allowances that track wages rise by the same %. CONDITIONAL: all unions must agree in-principle by 31.08.2026 to hold the 1 Aug date, else it shifts to the first of the month agreement is reached. NOT applied yet — do not change rates until certified. When certified, the EBA rise builds a SEPARATE agreement ladder — it must NOT be added to block A. Block A is the AWARD ladder; it moves only at a State Wage Case / reprint (~1 Sep). The certification (~1 Aug) and the SWC (~1 Sep) are only 31 days apart, so bumping block A on certification would be overwritten a month later = double-bump. Correct method: 1) build an Agreement-rate column = (award rate at 31.07.2026) × the agreed % for each row; 2) operational rate + $379 cap × same %; 3) set pay = MAX(award, agreement) per row (cl 2.18(6)); 4) block A itself changes ONLY at the SWC/reprint; 5) pull the Rates-checked-until tripwire back to the first-rise date (1 Aug if unions agree by 31 Aug); 6) footer date. Do NOT index: retention (cl 2.12(5) — not subject to annual increase, stays $45.00), shift % (a % of earnings — self-indexes; only change if the certified % changes), qualification (cl 4.2 — no indexation clause, hold pending certified text), in-charge/laundry (move with the award/SWC, not the EBA). YEARS 2-3: each 1 Aug, agreement ladder × 1.025 applied to the PRECEDING AGREEMENT rate (offer wording), NOT the award. After each 1 Sep SWC the award ladder moves independently — keep BOTH ladders live and re-check the MAX winner per row. Caution: if an SWC is ever a flat dollar amount or tiered (not a flat %), the winning ladder can differ by classification — don't assume a blanket MAX. If certification lands after 1 Aug, the first rise backdates and arrives lump-sum-taxed — use the 'Other taxable earnings' row and point to the Pay Guide lump-sum explainer.</t>
+    <t xml:space="preserve">OFFER 16.07.2026 — confirmed delayed, not certified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed delayed (as at 05.08.2026): the department has not responded to the unions’ claims and industrial action is ongoing. Employer Offer dated 16.07.2026 (3-year term, expires 31.07.2029). Three increases: 1 Aug 2026 = 3.5% (3% + 0.5% CPI uplift, already triggered), 1 Aug 2027 = 2.5%, 1 Aug 2028 = 2.5%. The FIRST rise applies to the higher of Award or Agreement — i.e. the Award rate (cl 2.18(6) retained). Allowances that track wages rise by the same %. CONDITIONAL: all unions must agree in-principle by 31.08.2026 to hold the 1 Aug date, else it shifts to the first of the month agreement is reached. NOT applied yet — do not change rates until certified. When certified, the EBA rise builds a SEPARATE agreement ladder — it must NOT be added to block A. Block A is the AWARD ladder; it moves only at a State Wage Case / reprint (~1 Sep). The certification (~1 Aug) and the SWC (~1 Sep) are only 31 days apart, so bumping block A on certification would be overwritten a month later = double-bump. Correct method: 1) build an Agreement-rate column = (award rate at 31.07.2026) × the agreed % for each row; 2) operational rate + $379 cap × same %; 3) set pay = MAX(award, agreement) per row (cl 2.18(6)); 4) block A itself changes ONLY at the SWC/reprint; 5) pull the Rates-checked-until tripwire back to the first-rise date (1 Aug if unions agree by 31 Aug); 6) footer date. Do NOT index: retention (cl 2.12(5) — not subject to annual increase, stays $45.00), shift % (a % of earnings — self-indexes; only change if the certified % changes), qualification (cl 4.2 — no indexation clause, hold pending certified text), in-charge/laundry (move with the award/SWC, not the EBA). YEARS 2-3: each 1 Aug, agreement ladder × 1.025 applied to the PRECEDING AGREEMENT rate (offer wording), NOT the award. After each 1 Sep SWC the award ladder moves independently — keep BOTH ladders live and re-check the MAX winner per row. Caution: if an SWC is ever a flat dollar amount or tiered (not a flat %), the winning ladder can differ by classification — don't assume a blanket MAX. If certification lands after 1 Aug, the first rise backdates and arrives lump-sum-taxed — use the 'Other taxable earnings' row and point to the Pay Guide lump-sum explainer.</t>
   </si>
   <si>
     <t xml:space="preserve">State Wage Case 2026</t>
@@ -3937,8 +3937,8 @@
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
       <c r="H62" s="8" t="str">
-        <f aca="false">IF($E$62="No — after-tax","Remserv can take your standard 5% pre-tax instead — the same percentage, but it leaves before income tax",TEXT($E$69,"0.00%")&amp;" of base, pre-tax — the fund's 15% tax then leaves "&amp;TEXT($E$69*(1-ContribTax),"0.00%")&amp;" in your account")</f>
-        <v>Remserv can take your standard 5% pre-tax instead — the same percentage, but it leaves before income tax</v>
+        <f aca="false">IF($E$62="No — after-tax","RemServ can take your standard 5% pre-tax instead — the same percentage, but it leaves before income tax",TEXT($E$69,"0.00%")&amp;" of base, pre-tax — the fund's 15% tax then leaves "&amp;TEXT($E$69*(1-ContribTax),"0.00%")&amp;" in your account")</f>
+        <v>RemServ can take your standard 5% pre-tax instead — the same percentage, but it leaves before income tax</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="49" t="n">
@@ -4808,7 +4808,7 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" prompt="Any extra taxable amount for this fortnight not covered above — e.g. a secondee travel/meal allowance, or a taxable one-off. Added to gross and taxed as wages; excluded from the super base (not OTE). A tax-free reimbursement instead? Use the custom pre-ta" promptTitle="Other taxable earnings" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="F56" type="decimal">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" prompt="Any extra taxable amount for this fortnight not covered above — e.g. a secondee travel/meal allowance, or a taxable one-off. Added to gross and taxed as wages; excluded from the super base (not OTE). A genuine tax-free reimbursement does not belong here — leave it out." promptTitle="Other taxable earnings" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="F56" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4836,7 +4836,7 @@
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Yes runs your member % through pre-tax pay (Remserv). Payroll does not gross it up — the full typed percentage is what lands. If you were quoted a grossed-up figure like 5.88 (5 ÷ 0.85), type that instead. More take-home, same super." promptTitle="Package the standard 5%?" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="E62" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Yes runs your member % through pre-tax pay (RemServ). Payroll does not gross it up — the full typed percentage is what lands. If you were quoted a grossed-up figure like 5.88 (5 ÷ 0.85), type that instead. More take-home, same super." promptTitle="Package the standard 5%?" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="E62" type="list">
       <formula1>"No — after-tax,Yes — pre-tax"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4844,7 +4844,7 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Annual &amp; long service carry shift + operational + retention. Special drops shift. Sick keeps retention only." promptTitle="Leave type" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="C14" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Pays base rate. Which allowances keep paying depends on the leave type — the Pay Guide tab has the full breakdown." promptTitle="Leave type" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="C14" type="list">
       <formula1>"No leave,Sick / carer's,Annual / recreation,Long service,Special"</formula1>
       <formula2>0</formula2>
     </dataValidation>
